--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/2mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/2mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X29"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.61016421297</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>412.896630473256</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>406.0431682390105</v>
+        <v>0.252976008</v>
+      </c>
+      <c r="Y2">
+        <v>0.262288458</v>
+      </c>
+      <c r="Z2">
+        <v>0.3644064980535252</v>
+      </c>
+      <c r="AA2">
+        <v>4.656225000000006</v>
+      </c>
+      <c r="AB2">
+        <v>0.07889850971389864</v>
+      </c>
+      <c r="AC2">
+        <v>32.57692881023021</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.6102799537</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>411.7613244927904</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>407.8262252772824</v>
+      </c>
+      <c r="X3">
+        <v>0.253023376</v>
+      </c>
+      <c r="Y3">
+        <v>0.262308514</v>
+      </c>
+      <c r="Z3">
+        <v>0.3644538178141719</v>
+      </c>
+      <c r="AA3">
+        <v>4.642569000000002</v>
+      </c>
+      <c r="AB3">
+        <v>0.0791369757680673</v>
+      </c>
+      <c r="AC3">
+        <v>32.58554595861325</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.61039569444</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>411.7689714317977</v>
       </c>
-      <c r="V4">
-        <v>0.6532729213659471</v>
-      </c>
-      <c r="W4" t="b">
+      <c r="V4" t="b">
         <v>1</v>
       </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.253058026</v>
+      </c>
+      <c r="Y4">
+        <v>0.2623187</v>
+      </c>
+      <c r="Z4">
+        <v>0.3644852053138875</v>
+      </c>
+      <c r="AA4">
+        <v>4.630337000000004</v>
+      </c>
+      <c r="AB4">
+        <v>0.07934942337389188</v>
+      </c>
+      <c r="AC4">
+        <v>32.67363044637371</v>
+      </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.61051201389</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>409.6855944795982</v>
       </c>
-      <c r="V5">
-        <v>1.200636851029387</v>
-      </c>
-      <c r="W5" t="b">
+      <c r="V5" t="b">
         <v>1</v>
       </c>
+      <c r="W5">
+        <v>32.64973087008466</v>
+      </c>
+      <c r="X5">
+        <v>0.253097446</v>
+      </c>
+      <c r="Y5">
+        <v>0.262340346</v>
+      </c>
+      <c r="Z5">
+        <v>0.3645281529746676</v>
+      </c>
+      <c r="AA5">
+        <v>4.621449999999996</v>
+      </c>
+      <c r="AB5">
+        <v>0.0795088096387305</v>
+      </c>
+      <c r="AC5">
+        <v>32.57361394320851</v>
+      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.61062833334</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>409.5292866379499</v>
       </c>
-      <c r="V6">
-        <v>1.25040524378491</v>
-      </c>
-      <c r="W6" t="b">
+      <c r="V6" t="b">
         <v>1</v>
       </c>
+      <c r="X6">
+        <v>0.253123196</v>
+      </c>
+      <c r="Y6">
+        <v>0.262365496</v>
+      </c>
+      <c r="Z6">
+        <v>0.3645641313192789</v>
+      </c>
+      <c r="AA6">
+        <v>4.62115</v>
+      </c>
+      <c r="AB6">
+        <v>0.07952161338856863</v>
+      </c>
+      <c r="AC6">
+        <v>32.56642960331936</v>
+      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.61074465277</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>409.0283269927191</v>
       </c>
-      <c r="V7">
-        <v>0.3433640577232134</v>
-      </c>
-      <c r="W7" t="b">
+      <c r="V7" t="b">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>0.253151172</v>
+      </c>
+      <c r="Y7">
+        <v>0.262376</v>
+      </c>
+      <c r="Z7">
+        <v>0.3645911151700951</v>
+      </c>
+      <c r="AA7">
+        <v>4.612414000000001</v>
+      </c>
+      <c r="AB7">
+        <v>0.07967565329095812</v>
+      </c>
+      <c r="AC7">
+        <v>32.58959916765254</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.61086097222</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>410.372647967966</v>
       </c>
-      <c r="V8">
-        <v>0.6793891599080265</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.253177876</v>
+      </c>
+      <c r="Y8">
+        <v>0.262388096</v>
+      </c>
+      <c r="Z8">
+        <v>0.3646183618776989</v>
+      </c>
+      <c r="AA8">
+        <v>4.605110000000003</v>
+      </c>
+      <c r="AB8">
+        <v>0.07980590487951057</v>
+      </c>
+      <c r="AC8">
+        <v>32.75016050888437</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.61097729167</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>408.8692363056267</v>
       </c>
-      <c r="V9">
-        <v>0.8259091311664019</v>
-      </c>
-      <c r="W9" t="b">
+      <c r="V9" t="b">
         <v>1</v>
       </c>
+      <c r="X9">
+        <v>0.253195996</v>
+      </c>
+      <c r="Y9">
+        <v>0.262400194</v>
+      </c>
+      <c r="Z9">
+        <v>0.3646396497936965</v>
+      </c>
+      <c r="AA9">
+        <v>4.602099000000003</v>
+      </c>
+      <c r="AB9">
+        <v>0.07986188895315063</v>
+      </c>
+      <c r="AC9">
+        <v>32.65306954619946</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.61109361111</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>409.0487231213538</v>
       </c>
-      <c r="V10">
-        <v>0.8211008000394991</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
       </c>
+      <c r="X10">
+        <v>0.25321825</v>
+      </c>
+      <c r="Y10">
+        <v>0.262418658</v>
+      </c>
+      <c r="Z10">
+        <v>0.3646683893615999</v>
+      </c>
+      <c r="AA10">
+        <v>4.600203999999998</v>
+      </c>
+      <c r="AB10">
+        <v>0.07990046973962808</v>
+      </c>
+      <c r="AC10">
+        <v>32.68318512379123</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.61120935185</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>409.0495117941396</v>
       </c>
-      <c r="V11">
-        <v>0.1038551802441441</v>
-      </c>
-      <c r="W11" t="b">
+      <c r="V11" t="b">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>0.25324114</v>
+      </c>
+      <c r="Y11">
+        <v>0.262427888</v>
+      </c>
+      <c r="Z11">
+        <v>0.3646909258380857</v>
+      </c>
+      <c r="AA11">
+        <v>4.593373999999997</v>
+      </c>
+      <c r="AB11">
+        <v>0.08002228392784339</v>
+      </c>
+      <c r="AC11">
+        <v>32.73307617333636</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.6113256713</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>407.5613100331082</v>
       </c>
-      <c r="V12">
-        <v>0.8589861076315619</v>
-      </c>
-      <c r="W12" t="b">
+      <c r="V12" t="b">
         <v>1</v>
       </c>
+      <c r="X12">
+        <v>0.253263076</v>
+      </c>
+      <c r="Y12">
+        <v>0.262453038</v>
+      </c>
+      <c r="Z12">
+        <v>0.3647242558706663</v>
+      </c>
+      <c r="AA12">
+        <v>4.594981000000004</v>
+      </c>
+      <c r="AB12">
+        <v>0.0800019315763825</v>
+      </c>
+      <c r="AC12">
+        <v>32.60569203844953</v>
+      </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.61144199074</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>407.6368828885135</v>
       </c>
-      <c r="V13">
-        <v>0.8382497800993129</v>
-      </c>
-      <c r="W13" t="b">
+      <c r="V13" t="b">
         <v>1</v>
       </c>
+      <c r="X13">
+        <v>0.253277064</v>
+      </c>
+      <c r="Y13">
+        <v>0.262453674</v>
+      </c>
+      <c r="Z13">
+        <v>0.3647344268705086</v>
+      </c>
+      <c r="AA13">
+        <v>4.588305000000005</v>
+      </c>
+      <c r="AB13">
+        <v>0.08011871664737935</v>
+      </c>
+      <c r="AC13">
+        <v>32.65934391516577</v>
+      </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.61155773148</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>408.5723050586814</v>
       </c>
-      <c r="V14">
-        <v>0.5631513761336228</v>
-      </c>
-      <c r="W14" t="b">
+      <c r="V14" t="b">
         <v>1</v>
       </c>
+      <c r="X14">
+        <v>0.253273884</v>
+      </c>
+      <c r="Y14">
+        <v>0.26245463</v>
+      </c>
+      <c r="Z14">
+        <v>0.3647329065561296</v>
+      </c>
+      <c r="AA14">
+        <v>4.590373</v>
+      </c>
+      <c r="AB14">
+        <v>0.08008285634175119</v>
+      </c>
+      <c r="AC14">
+        <v>32.71963721123253</v>
+      </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.61167405092</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>408.7492007402626</v>
       </c>
-      <c r="V15">
-        <v>0.5977119877668466</v>
-      </c>
-      <c r="W15" t="b">
+      <c r="V15" t="b">
         <v>1</v>
       </c>
+      <c r="X15">
+        <v>0.253298682</v>
+      </c>
+      <c r="Y15">
+        <v>0.262461314</v>
+      </c>
+      <c r="Z15">
+        <v>0.3647549364293014</v>
+      </c>
+      <c r="AA15">
+        <v>4.581316000000001</v>
+      </c>
+      <c r="AB15">
+        <v>0.08024348049531378</v>
+      </c>
+      <c r="AC15">
+        <v>32.79945851707635</v>
+      </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.61178979167</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>405.2028455210614</v>
       </c>
-      <c r="V16">
-        <v>1.998382053836452</v>
-      </c>
-      <c r="W16" t="b">
+      <c r="V16" t="b">
         <v>1</v>
       </c>
+      <c r="X16">
+        <v>0.25330949</v>
+      </c>
+      <c r="Y16">
+        <v>0.262460996</v>
+      </c>
+      <c r="Z16">
+        <v>0.3647622131545045</v>
+      </c>
+      <c r="AA16">
+        <v>4.575752999999999</v>
+      </c>
+      <c r="AB16">
+        <v>0.08034110073655136</v>
+      </c>
+      <c r="AC16">
+        <v>32.55444263074485</v>
+      </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.61190611111</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>406.2284169082748</v>
       </c>
-      <c r="V17">
-        <v>1.824955850545162</v>
-      </c>
-      <c r="W17" t="b">
+      <c r="V17" t="b">
         <v>1</v>
       </c>
+      <c r="X17">
+        <v>0.253297092</v>
+      </c>
+      <c r="Y17">
+        <v>0.26246195</v>
+      </c>
+      <c r="Z17">
+        <v>0.364754289917828</v>
+      </c>
+      <c r="AA17">
+        <v>4.582428999999998</v>
+      </c>
+      <c r="AB17">
+        <v>0.08022415335058612</v>
+      </c>
+      <c r="AC17">
+        <v>32.58933081341527</v>
+      </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.61202243056</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>406.6667317096869</v>
       </c>
-      <c r="V18">
-        <v>0.7513187637584717</v>
-      </c>
-      <c r="W18" t="b">
+      <c r="V18" t="b">
         <v>1</v>
       </c>
+      <c r="X18">
+        <v>0.253314578</v>
+      </c>
+      <c r="Y18">
+        <v>0.262463542</v>
+      </c>
+      <c r="Z18">
+        <v>0.3647675784749844</v>
+      </c>
+      <c r="AA18">
+        <v>4.574482000000003</v>
+      </c>
+      <c r="AB18">
+        <v>0.08036424114261263</v>
+      </c>
+      <c r="AC18">
+        <v>32.68146329179544</v>
+      </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.61213817129</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>405.4806560260822</v>
       </c>
-      <c r="V19">
-        <v>0.5997279562864989</v>
-      </c>
-      <c r="W19" t="b">
+      <c r="V19" t="b">
         <v>1</v>
       </c>
+      <c r="X19">
+        <v>0.25332189</v>
+      </c>
+      <c r="Y19">
+        <v>0.262467682</v>
+      </c>
+      <c r="Z19">
+        <v>0.3647756352165331</v>
+      </c>
+      <c r="AA19">
+        <v>4.572896</v>
+      </c>
+      <c r="AB19">
+        <v>0.08039343023354775</v>
+      </c>
+      <c r="AC19">
+        <v>32.59798083128602</v>
+      </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.61225391204</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>405.1617266905538</v>
       </c>
-      <c r="V20">
-        <v>0.7930459797421824</v>
-      </c>
-      <c r="W20" t="b">
+      <c r="V20" t="b">
         <v>1</v>
       </c>
+      <c r="X20">
+        <v>0.253311398</v>
+      </c>
+      <c r="Y20">
+        <v>0.262457812</v>
+      </c>
+      <c r="Z20">
+        <v>0.3647612471693529</v>
+      </c>
+      <c r="AA20">
+        <v>4.573207000000004</v>
+      </c>
+      <c r="AB20">
+        <v>0.08038492596486188</v>
+      </c>
+      <c r="AC20">
+        <v>32.56889540381577</v>
+      </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.61237023148</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>406.640691086887</v>
       </c>
-      <c r="V21">
-        <v>0.7783243699314392</v>
-      </c>
-      <c r="W21" t="b">
+      <c r="V21" t="b">
         <v>1</v>
       </c>
+      <c r="X21">
+        <v>0.25331712</v>
+      </c>
+      <c r="Y21">
+        <v>0.26245081</v>
+      </c>
+      <c r="Z21">
+        <v>0.3647601827978905</v>
+      </c>
+      <c r="AA21">
+        <v>4.566845000000001</v>
+      </c>
+      <c r="AB21">
+        <v>0.08049494585248552</v>
+      </c>
+      <c r="AC21">
+        <v>32.73252041045627</v>
+      </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.61248597223</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>405.7779298880246</v>
       </c>
-      <c r="V22">
-        <v>0.742899606547868</v>
-      </c>
-      <c r="W22" t="b">
+      <c r="V22" t="b">
         <v>1</v>
       </c>
+      <c r="X22">
+        <v>0.253300906</v>
+      </c>
+      <c r="Y22">
+        <v>0.262449536</v>
+      </c>
+      <c r="Z22">
+        <v>0.3647480060631396</v>
+      </c>
+      <c r="AA22">
+        <v>4.574314999999999</v>
+      </c>
+      <c r="AB22">
+        <v>0.08036288415933508</v>
+      </c>
+      <c r="AC22">
+        <v>32.60948477400611</v>
+      </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.61260229167</v>
       </c>
@@ -2050,14 +2416,29 @@
       <c r="U23">
         <v>407.1875006729652</v>
       </c>
-      <c r="V23">
-        <v>0.7106625321304548</v>
-      </c>
-      <c r="W23" t="b">
+      <c r="V23" t="b">
         <v>1</v>
       </c>
+      <c r="X23">
+        <v>0.253307266</v>
+      </c>
+      <c r="Y23">
+        <v>0.2624489</v>
+      </c>
+      <c r="Z23">
+        <v>0.3647519652032114</v>
+      </c>
+      <c r="AA23">
+        <v>4.570816999999998</v>
+      </c>
+      <c r="AB23">
+        <v>0.08042429258301405</v>
+      </c>
+      <c r="AC23">
+        <v>32.74776669026878</v>
+      </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:29">
       <c r="A24" s="1">
         <v>46068.61271861111</v>
       </c>
@@ -2121,14 +2502,29 @@
       <c r="U24">
         <v>408.3160098723229</v>
       </c>
-      <c r="V24">
-        <v>1.271631027295651</v>
-      </c>
-      <c r="W24" t="b">
+      <c r="V24" t="b">
         <v>1</v>
       </c>
+      <c r="X24">
+        <v>0.253299636</v>
+      </c>
+      <c r="Y24">
+        <v>0.262446352</v>
+      </c>
+      <c r="Z24">
+        <v>0.3647448331036924</v>
+      </c>
+      <c r="AA24">
+        <v>4.573357999999999</v>
+      </c>
+      <c r="AB24">
+        <v>0.08037875176609494</v>
+      </c>
+      <c r="AC24">
+        <v>32.81993119964982</v>
+      </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:29">
       <c r="A25" s="1">
         <v>46068.61283435185</v>
       </c>
@@ -2192,14 +2588,29 @@
       <c r="U25">
         <v>404.6723740912261</v>
       </c>
-      <c r="V25">
-        <v>1.865273726136546</v>
-      </c>
-      <c r="W25" t="b">
+      <c r="V25" t="b">
         <v>1</v>
       </c>
+      <c r="X25">
+        <v>0.253297092</v>
+      </c>
+      <c r="Y25">
+        <v>0.262445398</v>
+      </c>
+      <c r="Z25">
+        <v>0.3647423799711721</v>
+      </c>
+      <c r="AA25">
+        <v>4.574152999999995</v>
+      </c>
+      <c r="AB25">
+        <v>0.08036446583762794</v>
+      </c>
+      <c r="AC25">
+        <v>32.52127918308613</v>
+      </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:29">
       <c r="A26" s="1">
         <v>46068.61295009259</v>
       </c>
@@ -2263,14 +2674,29 @@
       <c r="U26">
         <v>406.3142013234728</v>
       </c>
-      <c r="V26">
-        <v>1.824779248387887</v>
-      </c>
-      <c r="W26" t="b">
+      <c r="V26" t="b">
         <v>1</v>
       </c>
+      <c r="X26">
+        <v>0.253299636</v>
+      </c>
+      <c r="Y26">
+        <v>0.262450172</v>
+      </c>
+      <c r="Z26">
+        <v>0.3647475817336724</v>
+      </c>
+      <c r="AA26">
+        <v>4.575267999999994</v>
+      </c>
+      <c r="AB26">
+        <v>0.0803463122631656</v>
+      </c>
+      <c r="AC26">
+        <v>32.64584769649449</v>
+      </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:29">
       <c r="A27" s="1">
         <v>46068.61306641204</v>
       </c>
@@ -2334,14 +2760,29 @@
       <c r="U27">
         <v>405.1049934047496</v>
       </c>
-      <c r="V27">
-        <v>0.8509739441448272</v>
-      </c>
-      <c r="W27" t="b">
+      <c r="V27" t="b">
         <v>1</v>
       </c>
+      <c r="X27">
+        <v>0.253302178</v>
+      </c>
+      <c r="Y27">
+        <v>0.262444124</v>
+      </c>
+      <c r="Z27">
+        <v>0.3647449953072298</v>
+      </c>
+      <c r="AA27">
+        <v>4.570973000000002</v>
+      </c>
+      <c r="AB27">
+        <v>0.08042007728415029</v>
+      </c>
+      <c r="AC27">
+        <v>32.57857487780515</v>
+      </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:29">
       <c r="A28" s="1">
         <v>46068.61318273148</v>
       </c>
@@ -2405,14 +2846,29 @@
       <c r="U28">
         <v>404.5636430555723</v>
       </c>
-      <c r="V28">
-        <v>0.8962605871591318</v>
-      </c>
-      <c r="W28" t="b">
+      <c r="V28" t="b">
         <v>1</v>
       </c>
+      <c r="X28">
+        <v>0.253304404</v>
+      </c>
+      <c r="Y28">
+        <v>0.262434892</v>
+      </c>
+      <c r="Z28">
+        <v>0.3647398985919239</v>
+      </c>
+      <c r="AA28">
+        <v>4.565244</v>
+      </c>
+      <c r="AB28">
+        <v>0.08051833050329395</v>
+      </c>
+      <c r="AC28">
+        <v>32.57478912116521</v>
+      </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:29">
       <c r="A29" s="1">
         <v>46068.61329847222</v>
       </c>
@@ -2476,11 +2932,26 @@
       <c r="U29">
         <v>407.2866350952676</v>
       </c>
-      <c r="V29">
-        <v>1.441486866317852</v>
-      </c>
-      <c r="W29" t="b">
+      <c r="V29" t="b">
         <v>1</v>
+      </c>
+      <c r="X29">
+        <v>0.253305358</v>
+      </c>
+      <c r="Y29">
+        <v>0.262433938</v>
+      </c>
+      <c r="Z29">
+        <v>0.3647398747130563</v>
+      </c>
+      <c r="AA29">
+        <v>4.56429</v>
+      </c>
+      <c r="AB29">
+        <v>0.08053489520267655</v>
+      </c>
+      <c r="AC29">
+        <v>32.80078647484814</v>
       </c>
     </row>
   </sheetData>
